--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1228 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2713,1339 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4044,6 +4044,783 @@
       </c>
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4719,22 +4719,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4826,6 +4826,339 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5159,6 +5159,561 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5714,6 +5714,1005 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       <c r="AB38" s="2" t="inlineStr"/>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       <c r="AB41" s="2" t="inlineStr"/>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6487,7 +6487,7 @@
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6598,7 +6598,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6709,7 +6709,562 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7268,6 +7268,561 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7823,6 +7823,561 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2263,13 +2263,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2384,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2445,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2485,13 +2489,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2610,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2721,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2782,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2832,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2943,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3004,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3040,13 +3048,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3119,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3146,7 +3158,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3157,7 +3169,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3280,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3341,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3379,7 +3391,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3502,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3563,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3595,13 +3607,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3728,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3789,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3823,7 +3839,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3950,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3995,7 +4011,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4045,7 +4061,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4172,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4233,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4256,7 +4272,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4267,7 +4283,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4344,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4378,7 +4394,7 @@
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4505,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4616,7 @@
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4677,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4711,7 +4727,7 @@
       <c r="AB38" s="2" t="inlineStr"/>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4788,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4811,7 +4827,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4822,7 +4838,7 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4949,7 @@
       <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4994,7 +5010,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5033,7 +5049,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5044,7 +5060,7 @@
       <c r="AB41" s="2" t="inlineStr"/>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5121,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5155,7 +5171,7 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5232,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5260,13 +5276,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5397,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5508,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5619,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5680,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5710,7 +5730,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5841,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5902,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5926,13 +5946,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6067,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6128,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6148,13 +6172,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6293,7 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6354,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6376,7 +6404,7 @@
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6515,7 @@
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6576,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6598,7 +6626,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6737,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6848,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6909,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -6931,7 +6959,7 @@
       <c r="AB58" s="2" t="inlineStr"/>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6992,7 +7020,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7042,7 +7070,7 @@
       <c r="AB59" s="2" t="inlineStr"/>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7070,32 +7098,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7103,7 +7135,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7127,17 +7159,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7147,13 +7179,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7300,7 @@
       <c r="AB61" s="2" t="inlineStr"/>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7292,32 +7328,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7325,7 +7365,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7349,17 +7389,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7369,13 +7409,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7403,32 +7447,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -7436,7 +7484,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7460,17 +7508,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7480,13 +7528,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7599,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7597,7 +7649,7 @@
       <c r="AB64" s="2" t="inlineStr"/>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7625,32 +7677,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>08:02</t>
@@ -7658,7 +7714,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7682,17 +7738,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -7702,13 +7758,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7829,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7819,7 +7879,7 @@
       <c r="AB66" s="2" t="inlineStr"/>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7940,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -7930,7 +7990,7 @@
       <c r="AB67" s="2" t="inlineStr"/>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7991,7 +8051,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8041,7 +8101,7 @@
       <c r="AB68" s="2" t="inlineStr"/>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8162,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8152,7 +8212,7 @@
       <c r="AB69" s="2" t="inlineStr"/>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8273,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8263,7 +8323,7 @@
       <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8384,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8374,7 +8434,562 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1042,13 +1042,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1220,7 +1224,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1263,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1331,7 +1335,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1553,7 +1557,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,7 +1668,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1779,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1814,7 +1818,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1886,7 +1890,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2108,7 +2112,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2223,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2258,7 +2262,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2273,7 +2277,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2503,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2675,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2710,7 +2714,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2782,7 +2786,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2826,13 +2830,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3012,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3058,7 +3066,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3127,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3230,7 +3238,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3269,7 +3277,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3341,7 +3349,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3385,13 +3393,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3464,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3491,7 +3503,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3563,7 +3575,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3612,12 +3624,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3690,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3717,7 +3729,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3789,7 +3801,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3900,7 +3912,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3939,7 +3951,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4011,7 +4023,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4055,13 +4067,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4138,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4161,7 +4177,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4233,7 +4249,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4344,7 +4360,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4455,7 +4471,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4494,7 +4510,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4677,7 +4693,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4788,7 +4804,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4899,7 +4915,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4938,7 +4954,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5010,7 +5026,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5286,7 +5302,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5474,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5497,7 +5513,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5680,7 +5696,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5724,13 +5740,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5922,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5956,7 +5976,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6037,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6056,7 +6076,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6128,7 +6148,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6177,12 +6197,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6263,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6282,7 +6302,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6354,7 +6374,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6398,13 +6418,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6489,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6504,7 +6528,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6576,7 +6600,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6909,7 +6933,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7135,7 +7159,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7174,7 +7198,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7189,7 +7213,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7443,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7508,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7538,7 +7562,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7566,32 +7590,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7599,7 +7627,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7623,17 +7651,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -7643,13 +7671,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7687,12 +7719,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -7714,7 +7746,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7763,12 +7795,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7796,32 +7828,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -7829,7 +7865,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7853,17 +7889,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -7873,13 +7909,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7907,32 +7947,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7940,7 +7984,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -7964,17 +8008,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -7984,13 +8028,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8099,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8162,7 +8210,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8273,7 +8321,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8384,7 +8432,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8495,7 +8543,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8606,7 +8654,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8717,7 +8765,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -8828,7 +8876,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -8939,7 +8987,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -8993,6 +9041,1009 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -820,13 +820,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -887,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -998,7 +1002,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1047,12 +1051,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1224,7 +1228,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1446,7 +1450,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1557,7 +1561,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1601,13 +1605,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1676,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1787,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2112,7 +2120,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,7 +2231,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2503,7 +2511,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2683,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,7 +2848,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3074,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3135,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3349,7 +3357,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3388,7 +3396,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3403,7 +3411,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3472,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3629,7 +3637,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3698,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3801,7 +3809,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3845,13 +3853,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3924,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4023,7 +4035,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4072,12 +4084,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4150,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4249,7 +4261,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4360,7 +4372,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4471,7 +4483,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4582,7 +4594,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4621,7 +4633,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4693,7 +4705,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4737,13 +4749,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4820,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4915,7 +4931,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5026,7 +5042,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,7 +5318,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5490,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5750,7 +5766,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5992,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6053,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6202,7 +6218,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6279,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6374,7 +6390,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6423,12 +6439,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6505,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6600,7 +6616,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6644,13 +6660,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6731,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6750,7 +6770,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -6933,7 +6953,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7159,7 +7179,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7443,7 +7463,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7582,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7701,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7820,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7885,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7904,7 +7924,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -7919,7 +7939,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7957,12 +7977,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -7984,7 +8004,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8033,12 +8053,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8066,32 +8086,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8099,7 +8123,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8123,17 +8147,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8143,13 +8167,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB68" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8177,32 +8205,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8210,7 +8242,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8234,17 +8266,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8254,13 +8286,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB69" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8357,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8432,7 +8468,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8543,7 +8579,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8654,7 +8690,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8876,7 +8912,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -8987,7 +9023,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9098,7 +9134,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9209,7 +9245,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9324,7 +9360,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9435,7 +9471,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9546,7 +9582,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9657,7 +9693,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9768,7 +9804,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -9879,7 +9915,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -9990,7 +10026,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10044,6 +10080,232 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1378,18 +1378,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1454,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1561,7 +1565,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1610,7 +1614,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1676,7 +1680,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,13 +1724,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1795,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1906,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,13 +1950,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2048,7 +2060,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2120,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2285,7 +2297,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2358,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2385,7 +2397,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2572,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2611,7 +2623,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2683,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,7 +2860,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3032,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3059,7 +3071,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3135,7 +3147,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3179,13 +3191,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3262,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3357,7 +3373,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3427,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3488,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3714,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3809,7 +3825,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3848,7 +3864,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3858,12 +3874,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3940,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4035,7 +4051,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4084,12 +4100,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4166,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4261,7 +4277,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4372,7 +4388,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4411,18 +4427,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4503,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4594,7 +4614,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4705,7 +4725,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4754,7 +4774,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -4820,7 +4840,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4864,13 +4884,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4955,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5042,7 +5066,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5153,7 +5177,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5192,7 +5216,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5379,7 +5403,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5418,7 +5442,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5490,7 +5514,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5601,7 +5625,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5640,7 +5664,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5766,7 +5790,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5962,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5977,7 +6001,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6053,7 +6077,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6279,7 +6303,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6390,7 +6414,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6439,12 +6463,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6529,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6616,7 +6640,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6665,7 +6689,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6731,7 +6755,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6953,7 +6977,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -6997,13 +7021,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7092,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7103,7 +7131,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7179,7 +7207,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7233,7 +7261,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7322,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7333,7 +7361,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7528,7 +7556,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7567,7 +7595,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7701,7 +7729,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7885,7 +7913,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -7939,7 +7967,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7977,24 +8005,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8004,7 +8032,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8053,12 +8081,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8096,24 +8124,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8123,7 +8151,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8162,7 +8190,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8172,12 +8200,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8215,12 +8243,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -8242,7 +8270,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8291,7 +8319,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8324,32 +8352,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8357,7 +8389,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8381,33 +8413,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8435,32 +8471,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8468,7 +8508,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8492,17 +8532,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8512,13 +8552,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8546,32 +8590,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -8579,7 +8627,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8603,17 +8651,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8623,13 +8671,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8657,12 +8709,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq41，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -8690,7 +8742,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8698,10 +8750,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8879,32 +8947,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8912,7 +8984,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -8936,17 +9008,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -8956,13 +9028,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9099,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9134,7 +9210,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9245,7 +9321,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9299,7 +9375,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9436,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9471,7 +9547,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9582,7 +9658,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9693,7 +9769,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9804,7 +9880,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -9915,7 +9991,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10026,7 +10102,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10137,7 +10213,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10248,7 +10324,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10302,7 +10378,685 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2176,13 +2176,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2247,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2287,17 +2291,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2508,7 +2512,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2584,7 +2588,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2699,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2921,7 +2925,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2960,7 +2964,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3032,7 +3036,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3151,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3186,7 +3190,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3196,12 +3200,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3266,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3373,7 +3377,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3492,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3532,13 +3536,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3722,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3825,7 +3833,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3879,7 +3887,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3948,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4105,7 +4113,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4174,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4277,7 +4285,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4388,7 +4396,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4437,12 +4445,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4511,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4614,7 +4622,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,7 +4848,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4879,7 +4887,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4889,12 +4897,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4963,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5066,7 +5074,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5110,13 +5118,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5300,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5327,7 +5339,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5403,7 +5415,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5514,7 +5526,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5625,7 +5637,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5851,7 +5863,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5890,7 +5902,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -5962,7 +5974,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6077,7 +6089,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6303,7 +6315,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6468,7 +6480,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6541,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6755,7 +6767,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6977,7 +6989,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7016,7 +7028,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7207,7 +7219,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7251,17 +7263,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7334,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7437,7 +7449,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7476,7 +7488,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7556,7 +7568,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7913,7 +7925,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8086,7 +8098,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8163,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8205,7 +8217,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8362,24 +8374,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8389,7 +8401,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8438,12 +8450,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8520,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8547,7 +8559,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8600,24 +8612,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8627,7 +8639,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8666,7 +8678,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -8676,12 +8688,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8726,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq41，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -8742,7 +8754,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8957,24 +8969,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8984,7 +8996,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9023,7 +9035,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9033,12 +9045,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9066,32 +9078,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9099,7 +9115,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9123,17 +9139,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9143,13 +9159,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9177,32 +9197,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>08:02</t>
@@ -9210,7 +9234,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9234,17 +9258,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9254,13 +9278,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9288,32 +9316,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9321,7 +9353,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9345,17 +9377,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9365,17 +9397,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9468,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9547,7 +9579,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9658,7 +9690,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9769,7 +9801,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9880,7 +9912,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -9991,7 +10023,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10102,7 +10134,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10213,7 +10245,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10324,7 +10356,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10550,7 +10582,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10661,7 +10693,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -10772,7 +10804,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -10826,7 +10858,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10919,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -10936,12 +10968,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11034,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11060,6 +11092,577 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,18 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -935,13 +939,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1267,18 +1275,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1351,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1454,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1680,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1734,7 +1746,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1834,18 +1846,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1922,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2132,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2171,7 +2187,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2181,12 +2197,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2263,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2286,7 +2302,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2296,12 +2312,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2699,7 +2715,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2738,18 +2754,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2849,7 +2869,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2925,7 +2945,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3056,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3151,7 +3171,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3286,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3305,18 +3325,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3401,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3492,7 +3516,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3531,7 +3555,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3546,7 +3570,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3746,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3761,18 +3785,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3861,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3948,7 +3976,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3987,18 +4015,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4206,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4218,13 +4250,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4432,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4511,7 +4547,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4550,18 +4586,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4662,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4888,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4902,7 +4942,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4963,7 +5003,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5002,18 +5042,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5118,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5113,7 +5157,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5123,12 +5167,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5344,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5415,7 +5459,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5526,7 +5570,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5565,18 +5609,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5796,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5787,7 +5835,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -5863,7 +5911,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5974,7 +6022,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6089,7 +6137,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6128,18 +6176,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6367,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6354,18 +6406,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6597,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6585,13 +6641,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6827,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6989,7 +7049,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7219,7 +7279,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7258,7 +7318,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7268,12 +7328,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7509,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7568,7 +7628,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7687,7 +7747,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7726,7 +7786,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -7925,7 +7985,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8163,7 +8223,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8401,7 +8461,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8520,7 +8580,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8639,7 +8699,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8693,7 +8753,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8996,7 +9056,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9088,24 +9148,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9115,7 +9175,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9154,7 +9214,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9164,12 +9224,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9294,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9273,7 +9333,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9288,7 +9348,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9326,12 +9386,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -9353,7 +9413,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9392,7 +9452,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9402,12 +9462,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9435,32 +9495,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9468,7 +9532,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9492,33 +9556,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB79" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9546,32 +9614,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -9579,7 +9651,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9603,33 +9675,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB80" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9657,32 +9733,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9690,7 +9770,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9714,33 +9794,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB81" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9768,32 +9852,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9801,7 +9889,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9825,33 +9913,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB82" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9879,32 +9971,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>08:11</t>
@@ -9912,7 +10008,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -9936,33 +10032,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB83" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9990,32 +10090,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10023,7 +10127,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10047,17 +10151,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10067,13 +10171,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB84" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10101,32 +10209,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10134,7 +10246,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10158,33 +10270,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB85" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10361,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10356,7 +10472,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10582,7 +10698,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10804,7 +10920,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -10919,7 +11035,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11034,7 +11150,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11149,7 +11265,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11264,7 +11380,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11375,7 +11491,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11490,7 +11606,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11552,22 +11668,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11600,12 +11716,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11619,47 +11735,1197 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB98" s="2" t="inlineStr">
+      <c r="AB99" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
         </is>
       </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>12/30</t>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC108"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,13 +1510,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1746,7 +1750,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1861,7 +1865,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2152,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2202,7 +2206,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2317,7 +2321,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2417,18 +2421,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2715,7 +2723,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2769,7 +2777,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2838,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2884,7 +2892,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2953,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2984,7 +2992,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3056,7 +3064,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,7 +3179,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3215,17 +3223,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3294,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3340,7 +3348,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3409,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3445,17 +3453,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3524,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3570,7 +3578,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3754,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3800,7 +3808,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3869,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3905,17 +3913,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3984,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4030,7 +4038,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4153,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4268,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4440,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4476,12 +4484,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4547,7 +4555,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4601,7 +4609,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4670,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4706,13 +4714,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4900,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4942,7 +4954,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5015,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5057,7 +5069,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5130,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5172,7 +5184,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5356,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5459,7 +5471,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5498,18 +5510,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5586,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5624,7 +5640,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5812,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5850,7 +5866,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5927,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5950,7 +5966,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6022,7 +6038,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6137,7 +6153,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6191,7 +6207,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6383,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6421,7 +6437,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6552,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6667,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6843,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6871,13 +6887,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6958,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7279,7 +7299,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7333,7 +7353,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7529,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7628,7 +7648,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7747,7 +7767,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7801,7 +7821,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7985,7 +8005,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8029,17 +8049,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8178,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8243,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8267,17 +8287,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8481,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8505,12 +8525,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8699,7 +8719,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8753,7 +8773,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8961,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9056,7 +9076,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9100,17 +9120,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9195,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9229,7 +9249,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9294,7 +9314,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9348,7 +9368,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9433,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9467,7 +9487,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9552,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9586,7 +9606,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9671,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9705,7 +9725,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9790,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9824,7 +9844,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9909,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9943,7 +9963,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10028,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10062,7 +10082,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10201,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10266,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10300,7 +10320,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10328,32 +10348,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -10361,7 +10385,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10385,17 +10409,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10405,13 +10429,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB86" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10439,32 +10467,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -10472,7 +10504,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10496,17 +10528,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10516,17 +10548,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10665,32 +10697,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10698,7 +10734,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10722,33 +10758,37 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB89" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10887,32 +10927,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10920,7 +10964,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -10944,17 +10988,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -10964,17 +11008,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11002,32 +11046,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11035,7 +11083,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11059,17 +11107,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11079,12 +11127,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11150,7 +11198,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11380,7 +11428,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11419,7 +11467,7 @@
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -11458,32 +11506,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -11491,7 +11543,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11515,17 +11567,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11535,17 +11587,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11658,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11721,7 +11773,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11775,7 +11827,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11888,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -11890,7 +11942,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11970,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq31，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -11951,7 +12003,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -11959,10 +12011,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12005,7 +12073,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12134,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12120,7 +12188,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12249,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12235,7 +12303,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12364,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12350,7 +12418,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12479,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12465,7 +12533,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12594,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12580,7 +12648,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12709,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12695,7 +12763,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12824,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -12810,7 +12878,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12939,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -12925,7 +12993,233 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-浦东35路.xlsx
+++ b/data/export/2026-10-29-浦东35路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2997,13 +2997,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3183,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3233,7 +3237,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3298,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3348,7 +3352,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3467,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3528,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3568,17 +3572,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3758,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3927,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3988,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4028,17 +4032,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4157,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4272,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4498,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4559,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4609,7 +4613,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4728,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4904,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4944,17 +4948,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5019,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5069,7 +5073,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5134,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5174,17 +5178,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5360,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5525,7 +5529,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5590,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5640,7 +5644,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5816,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5866,7 +5870,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5931,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5971,13 +5975,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6161,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6207,7 +6215,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6391,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6437,7 +6445,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6560,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6675,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6905,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6966,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7123,7 +7131,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7307,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7353,7 +7361,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7537,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7767,7 +7775,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7821,7 +7829,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8067,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8186,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8305,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8543,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8662,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8727,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8763,17 +8771,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8969,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9076,7 +9084,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9130,7 +9138,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9203,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9239,17 +9247,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9322,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9358,17 +9366,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9441,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9487,7 +9495,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9560,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9606,7 +9614,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9671,7 +9679,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9725,7 +9733,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9790,7 +9798,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9834,17 +9842,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9917,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -9963,7 +9971,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10036,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10082,7 +10090,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10209,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10274,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10320,7 +10328,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10447,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10566,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10742,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10788,7 +10796,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11026,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11145,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11375,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11395,32 +11403,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -11428,7 +11440,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11452,17 +11464,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11472,13 +11484,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11528,12 +11544,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11543,7 +11559,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11597,7 +11613,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11674,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11740,32 +11756,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:02</t>
@@ -11773,7 +11793,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11797,17 +11817,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -11817,17 +11837,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11855,32 +11875,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -11888,7 +11912,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -11912,17 +11936,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -11932,17 +11956,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11999,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq31，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq53，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12003,7 +12027,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12073,7 +12097,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12101,32 +12125,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12134,7 +12162,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12158,17 +12186,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12178,17 +12206,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12216,32 +12244,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12249,7 +12281,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12273,17 +12305,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12293,17 +12325,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12396,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12418,7 +12450,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12446,12 +12478,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq48，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12479,7 +12511,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12487,10 +12519,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
-      <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12533,7 +12581,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12642,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12648,7 +12696,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12757,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12763,7 +12811,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12872,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -12878,7 +12926,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12987,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -12993,7 +13041,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13102,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13108,7 +13156,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13217,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13213,13 +13261,17 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB110" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
